--- a/src/産業/産業.xlsx
+++ b/src/産業/産業.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kyont\private\WeldyAlin\ゲーム開発系\simutrans\128japan+\src\産業\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kyont\private\game_modding\simutrans\128japan+\src\産業\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB18461F-E932-4750-AC0C-AC8344453298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3C19EE-BDBF-453E-ACB3-E8DC6DAACEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="294">
   <si>
     <t>生産性</t>
     <rPh sb="0" eb="3">
@@ -1292,6 +1292,34 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>コウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新聞社</t>
+    <rPh sb="0" eb="3">
+      <t>シンブンシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新聞販売店</t>
+    <rPh sb="0" eb="5">
+      <t>シンブンハンバイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新聞販売店（1910）</t>
+    <rPh sb="0" eb="5">
+      <t>シンブンハンバイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新聞販売店（1960）</t>
+    <rPh sb="0" eb="5">
+      <t>シンブンハンバイテン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2726,7 +2754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2977,6 +3005,10 @@
     <xf numFmtId="0" fontId="0" fillId="220" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="218" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="160" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="208" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="212" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="214" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2985,16 +3017,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFECECEC"/>
+      <color rgb="FF606060"/>
+      <color rgb="FF202020"/>
+      <color rgb="FF765B82"/>
+      <color rgb="FF909090"/>
       <color rgb="FFFFC184"/>
       <color rgb="FF4B3E6C"/>
       <color rgb="FF716996"/>
       <color rgb="FF292936"/>
       <color rgb="FF400000"/>
-      <color rgb="FF00F1DB"/>
-      <color rgb="FF006AFF"/>
-      <color rgb="FFFF4040"/>
-      <color rgb="FF78C99C"/>
-      <color rgb="FF8A4010"/>
     </mruColors>
   </colors>
   <extLst>
@@ -3271,7 +3303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -4354,6 +4386,14 @@
       </c>
     </row>
     <row r="26" spans="1:16">
+      <c r="A26" s="247"/>
+      <c r="B26" t="str">
+        <f>VLOOKUP($C26,色!$A$2:$B$225,2,FALSE)</f>
+        <v>#ECECEC</v>
+      </c>
+      <c r="C26">
+        <v>214</v>
+      </c>
       <c r="D26" s="4" t="s">
         <v>13</v>
       </c>
@@ -4370,27 +4410,27 @@
         <v>15</v>
       </c>
       <c r="I26" s="2">
-        <f t="shared" ref="I26:I29" si="36">IF($E26="",14*64,$E26*64)</f>
+        <f t="shared" ref="I26:I32" si="36">IF($E26="",14*64,$E26*64)</f>
         <v>9600</v>
       </c>
       <c r="J26" s="4">
-        <f t="shared" ref="J26:J29" si="37">IF($E26="",(14+$F26)*64,($E26+$F26)*64)</f>
+        <f t="shared" ref="J26:J32" si="37">IF($E26="",(14+$F26)*64,($E26+$F26)*64)</f>
         <v>11520</v>
       </c>
       <c r="K26" s="2">
-        <f t="shared" ref="K26:K29" si="38">G26*72</f>
+        <f t="shared" ref="K26:K32" si="38">G26*72</f>
         <v>2304</v>
       </c>
       <c r="L26" t="str">
-        <f t="shared" ref="L26:L29" si="39">FIXED($K26*$J26/$I26,0,TRUE)</f>
+        <f t="shared" ref="L26:L32" si="39">FIXED($K26*$J26/$I26,0,TRUE)</f>
         <v>2765</v>
       </c>
       <c r="M26" s="4" t="str">
-        <f t="shared" ref="M26:M29" si="40">FIXED(($K26+$L26)/2,0,TRUE)</f>
+        <f t="shared" ref="M26:M32" si="40">FIXED(($K26+$L26)/2,0,TRUE)</f>
         <v>2535</v>
       </c>
       <c r="N26" s="2">
-        <f t="shared" ref="N26:N29" si="41">IF($H26="",$G26/3*72,$H26*72)</f>
+        <f t="shared" ref="N26:N32" si="41">IF($H26="",$G26/3*72,$H26*72)</f>
         <v>1080</v>
       </c>
       <c r="O26" t="str">
@@ -4398,11 +4438,19 @@
         <v>1296</v>
       </c>
       <c r="P26" t="str">
-        <f t="shared" ref="P26:P29" si="42">FIXED(($N26+$O26)/2,0,TRUE)</f>
+        <f t="shared" ref="P26:P32" si="42">FIXED(($N26+$O26)/2,0,TRUE)</f>
         <v>1188</v>
       </c>
     </row>
     <row r="27" spans="1:16">
+      <c r="A27" s="245"/>
+      <c r="B27" t="str">
+        <f>VLOOKUP($C27,色!$A$2:$B$225,2,FALSE)</f>
+        <v>#202020</v>
+      </c>
+      <c r="C27">
+        <v>208</v>
+      </c>
       <c r="D27" s="4" t="s">
         <v>14</v>
       </c>
@@ -4452,6 +4500,14 @@
       </c>
     </row>
     <row r="28" spans="1:16">
+      <c r="A28" s="245"/>
+      <c r="B28" t="str">
+        <f>VLOOKUP($C28,色!$A$2:$B$225,2,FALSE)</f>
+        <v>#202020</v>
+      </c>
+      <c r="C28">
+        <v>208</v>
+      </c>
       <c r="D28" s="4" t="s">
         <v>15</v>
       </c>
@@ -4501,153 +4557,332 @@
       </c>
     </row>
     <row r="29" spans="1:16">
+      <c r="A29" s="245"/>
+      <c r="B29" t="str">
+        <f>VLOOKUP($C29,色!$A$2:$B$225,2,FALSE)</f>
+        <v>#202020</v>
+      </c>
+      <c r="C29">
+        <v>208</v>
+      </c>
       <c r="D29" s="4" t="s">
-        <v>16</v>
+        <v>290</v>
       </c>
       <c r="E29">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="F29">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="G29">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H29">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="I29" s="2">
         <f t="shared" si="36"/>
-        <v>1600</v>
+        <v>32000</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="37"/>
-        <v>6400</v>
+        <v>40960</v>
       </c>
       <c r="K29" s="2">
         <f t="shared" si="38"/>
-        <v>1080</v>
+        <v>3600</v>
       </c>
       <c r="L29" t="str">
         <f t="shared" si="39"/>
-        <v>4320</v>
+        <v>4608</v>
       </c>
       <c r="M29" s="4" t="str">
         <f t="shared" si="40"/>
-        <v>2700</v>
+        <v>4104</v>
       </c>
       <c r="N29" s="2">
         <f t="shared" si="41"/>
-        <v>576</v>
+        <v>3240</v>
       </c>
       <c r="O29" t="str">
         <f>FIXED($N29*$J29/$I29,0,TRUE)</f>
-        <v>2304</v>
+        <v>4147</v>
       </c>
       <c r="P29" t="str">
         <f t="shared" si="42"/>
+        <v>3694</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="244"/>
+      <c r="B30" t="str">
+        <f>VLOOKUP($C30,色!$A$2:$B$225,2,FALSE)</f>
+        <v>#765B82</v>
+      </c>
+      <c r="C30">
+        <v>107</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30">
+        <v>25</v>
+      </c>
+      <c r="F30">
+        <v>75</v>
+      </c>
+      <c r="G30">
+        <v>15</v>
+      </c>
+      <c r="H30">
+        <v>8</v>
+      </c>
+      <c r="I30" s="2">
+        <f t="shared" si="36"/>
+        <v>1600</v>
+      </c>
+      <c r="J30" s="4">
+        <f t="shared" si="37"/>
+        <v>6400</v>
+      </c>
+      <c r="K30" s="2">
+        <f t="shared" si="38"/>
+        <v>1080</v>
+      </c>
+      <c r="L30" t="str">
+        <f t="shared" si="39"/>
+        <v>4320</v>
+      </c>
+      <c r="M30" s="4" t="str">
+        <f t="shared" si="40"/>
+        <v>2700</v>
+      </c>
+      <c r="N30" s="2">
+        <f t="shared" si="41"/>
+        <v>576</v>
+      </c>
+      <c r="O30" t="str">
+        <f>FIXED($N30*$J30/$I30,0,TRUE)</f>
+        <v>2304</v>
+      </c>
+      <c r="P30" t="str">
+        <f t="shared" si="42"/>
         <v>1440</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
-      <c r="D30" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
     <row r="31" spans="1:16">
+      <c r="A31" s="246"/>
+      <c r="B31" t="str">
+        <f>VLOOKUP($C31,色!$A$2:$B$225,2,FALSE)</f>
+        <v>#606060</v>
+      </c>
+      <c r="C31">
+        <v>212</v>
+      </c>
       <c r="D31" s="4" t="s">
-        <v>11</v>
+        <v>292</v>
       </c>
       <c r="E31">
-        <v>450</v>
+        <v>15</v>
       </c>
       <c r="F31">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I31" s="2">
-        <f t="shared" ref="I31" si="43">IF($E31="",14*64,$E31*64)</f>
-        <v>28800</v>
+        <f t="shared" si="36"/>
+        <v>960</v>
       </c>
       <c r="J31" s="4">
-        <f t="shared" ref="J31" si="44">IF($E31="",(14+$F31)*64,($E31+$F31)*64)</f>
-        <v>38400</v>
+        <f t="shared" si="37"/>
+        <v>1024</v>
       </c>
       <c r="K31" s="2">
-        <f t="shared" ref="K31:K32" si="45">G31*72</f>
-        <v>3600</v>
+        <f t="shared" si="38"/>
+        <v>216</v>
       </c>
       <c r="L31" t="str">
-        <f>FIXED($K31*$J31/$I31,0,TRUE)</f>
-        <v>4800</v>
+        <f t="shared" si="39"/>
+        <v>230</v>
       </c>
       <c r="M31" s="4" t="str">
-        <f t="shared" ref="M31:M32" si="46">FIXED(($K31+$L31)/2,0,TRUE)</f>
-        <v>4200</v>
+        <f t="shared" si="40"/>
+        <v>223</v>
       </c>
       <c r="N31" s="2">
-        <f t="shared" ref="N31:N32" si="47">IF($H31="",$G31/3*72,$H31*72)</f>
-        <v>1224</v>
+        <f t="shared" si="41"/>
+        <v>72</v>
       </c>
       <c r="O31" t="str">
         <f>FIXED($N31*$J31/$I31,0,TRUE)</f>
+        <v>77</v>
+      </c>
+      <c r="P31" t="str">
+        <f t="shared" si="42"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="246"/>
+      <c r="B32" t="str">
+        <f>VLOOKUP($C32,色!$A$2:$B$225,2,FALSE)</f>
+        <v>#606060</v>
+      </c>
+      <c r="C32">
+        <v>212</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E32">
+        <v>25</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>6</v>
+      </c>
+      <c r="H32">
+        <v>2</v>
+      </c>
+      <c r="I32" s="2">
+        <f t="shared" si="36"/>
+        <v>1600</v>
+      </c>
+      <c r="J32" s="4">
+        <f t="shared" si="37"/>
+        <v>1920</v>
+      </c>
+      <c r="K32" s="2">
+        <f t="shared" si="38"/>
+        <v>432</v>
+      </c>
+      <c r="L32" t="str">
+        <f t="shared" si="39"/>
+        <v>518</v>
+      </c>
+      <c r="M32" s="4" t="str">
+        <f t="shared" si="40"/>
+        <v>475</v>
+      </c>
+      <c r="N32" s="2">
+        <f t="shared" si="41"/>
+        <v>144</v>
+      </c>
+      <c r="O32" t="str">
+        <f>FIXED($N32*$J32/$I32,0,TRUE)</f>
+        <v>173</v>
+      </c>
+      <c r="P32" t="str">
+        <f t="shared" si="42"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="4:16">
+      <c r="D33" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="4:16">
+      <c r="D34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34">
+        <v>450</v>
+      </c>
+      <c r="F34">
+        <v>150</v>
+      </c>
+      <c r="G34">
+        <v>50</v>
+      </c>
+      <c r="H34">
+        <v>17</v>
+      </c>
+      <c r="I34" s="2">
+        <f t="shared" ref="I34" si="43">IF($E34="",14*64,$E34*64)</f>
+        <v>28800</v>
+      </c>
+      <c r="J34" s="4">
+        <f t="shared" ref="J34" si="44">IF($E34="",(14+$F34)*64,($E34+$F34)*64)</f>
+        <v>38400</v>
+      </c>
+      <c r="K34" s="2">
+        <f t="shared" ref="K34:K35" si="45">G34*72</f>
+        <v>3600</v>
+      </c>
+      <c r="L34" t="str">
+        <f>FIXED($K34*$J34/$I34,0,TRUE)</f>
+        <v>4800</v>
+      </c>
+      <c r="M34" s="4" t="str">
+        <f t="shared" ref="M34:M35" si="46">FIXED(($K34+$L34)/2,0,TRUE)</f>
+        <v>4200</v>
+      </c>
+      <c r="N34" s="2">
+        <f t="shared" ref="N34:N35" si="47">IF($H34="",$G34/3*72,$H34*72)</f>
+        <v>1224</v>
+      </c>
+      <c r="O34" t="str">
+        <f>FIXED($N34*$J34/$I34,0,TRUE)</f>
         <v>1632</v>
       </c>
-      <c r="P31" t="str">
-        <f t="shared" ref="P31:P32" si="48">FIXED(($N31+$O31)/2,0,TRUE)</f>
+      <c r="P34" t="str">
+        <f t="shared" ref="P34:P35" si="48">FIXED(($N34+$O34)/2,0,TRUE)</f>
         <v>1428</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
-      <c r="D32" s="4" t="s">
+    <row r="35" spans="4:16">
+      <c r="D35" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E32">
+      <c r="E35">
         <v>32</v>
       </c>
-      <c r="F32">
+      <c r="F35">
         <v>64</v>
       </c>
-      <c r="G32">
+      <c r="G35">
         <v>15</v>
       </c>
-      <c r="H32">
+      <c r="H35">
         <v>5</v>
       </c>
-      <c r="I32" s="2">
-        <f>IF($E32="",14*64,$E32*64)</f>
+      <c r="I35" s="2">
+        <f>IF($E35="",14*64,$E35*64)</f>
         <v>2048</v>
       </c>
-      <c r="J32" s="4">
-        <f>IF($E32="",(14+$F32)*64,($E32+$F32)*64)</f>
+      <c r="J35" s="4">
+        <f>IF($E35="",(14+$F35)*64,($E35+$F35)*64)</f>
         <v>6144</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K35" s="2">
         <f t="shared" si="45"/>
         <v>1080</v>
       </c>
-      <c r="L32" t="str">
-        <f>FIXED($K32*$J32/$I32,0,TRUE)</f>
+      <c r="L35" t="str">
+        <f>FIXED($K35*$J35/$I35,0,TRUE)</f>
         <v>3240</v>
       </c>
-      <c r="M32" s="4" t="str">
+      <c r="M35" s="4" t="str">
         <f t="shared" si="46"/>
         <v>2160</v>
       </c>
-      <c r="N32" s="2">
+      <c r="N35" s="2">
         <f t="shared" si="47"/>
         <v>360</v>
       </c>
-      <c r="O32" t="str">
-        <f>FIXED($N32*$J32/$I32,0,TRUE)</f>
+      <c r="O35" t="str">
+        <f>FIXED($N35*$J35/$I35,0,TRUE)</f>
         <v>1080</v>
       </c>
-      <c r="P32" t="str">
+      <c r="P35" t="str">
         <f t="shared" si="48"/>
         <v>720</v>
       </c>
@@ -4660,7 +4895,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B90F1B2-CB39-42F5-A16E-826A07F4787A}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="27.25" style="4" bestFit="1" customWidth="1"/>
@@ -4791,41 +5026,41 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>291</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>283</v>
       </c>
       <c r="E8">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
         <v>44</v>
@@ -4842,10 +5077,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -4854,15 +5089,15 @@
         <v>52</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -4871,12 +5106,12 @@
         <v>52</v>
       </c>
       <c r="E12">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>279</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
         <v>47</v>
@@ -4885,32 +5120,32 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>52</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>22</v>
+        <v>279</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>280</v>
       </c>
       <c r="E14">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
         <v>48</v>
@@ -4919,18 +5154,18 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -4944,7 +5179,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
         <v>49</v>
@@ -4953,15 +5188,15 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E17">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>49</v>
@@ -4970,7 +5205,7 @@
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E18">
         <v>16</v>
@@ -4978,16 +5213,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E19">
         <v>16</v>
@@ -4995,33 +5230,33 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
-        <v>10</v>
+        <v>290</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>283</v>
       </c>
       <c r="E20">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E21">
         <v>16</v>
@@ -5029,27 +5264,27 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E22">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -5058,15 +5293,15 @@
         <v>52</v>
       </c>
       <c r="E23">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -5075,15 +5310,15 @@
         <v>52</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -5092,6 +5327,40 @@
         <v>52</v>
       </c>
       <c r="E25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27">
         <v>16</v>
       </c>
     </row>
@@ -5102,10 +5371,10 @@
       <sortCondition ref="B2:B23"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E25">
-    <sortCondition descending="1" ref="C2:C25"/>
-    <sortCondition ref="B2:B25"/>
-    <sortCondition descending="1" ref="E2:E25"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E27">
+    <sortCondition descending="1" ref="C2:C27"/>
+    <sortCondition ref="B2:B27"/>
+    <sortCondition descending="1" ref="E2:E27"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
